--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T01:04:27+00:00</t>
+    <t>2026-10-19T02:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Specific determination describes the qualitative detection of a predefined microbial target in a specimen by direct molecular, immunological or biochemical detection methods and by method-neutrally coded detection tests. Culture-based targeted detection also belongs here; the procedure is stated in the investigation code and in Observation.method.</t>
+    <t>Specific determination describes the qualitative detection of a predefined microbial target in a specimen by direct molecular, immunological or biochemical detection methods and by detection tests with method-neutral codes. Culture-based targeted detection also belongs here; the procedure is stated in the investigation code and in Observation.method.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T02:33:36+00:00</t>
+    <t>2026-10-19T02:49:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
